--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-input-tddui-task-transport-valueset.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-input-tddui-task-transport-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T10:31:14+00:00</t>
+    <t>2026-02-04T11:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-input-tddui-task-transport-valueset.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-input-tddui-task-transport-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-input-tddui-task-transport-valueset.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-input-tddui-task-transport-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
